--- a/reports/셀린느/history/2026-06-10/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/history/2026-06-10/셀린느_league_mgf_report.xlsx
@@ -137,10 +137,10 @@
     <t>Scania 16</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>12경 4301조 343억 8536만</t>
+    <t>33</t>
+  </si>
+  <si>
+    <t>12경 5115조 9442억 4070만</t>
   </si>
   <si>
     <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
@@ -164,7 +164,7 @@
     <t>3위</t>
   </si>
   <si>
-    <t>16경 5903조 2011억 8275만</t>
+    <t>16경 6372조 2841억 4048만</t>
   </si>
   <si>
     <t>길컨에 진심인 길드입니다 300조 이상 무치z / 연지임당 으로 문의주세요</t>
@@ -920,7 +920,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>1경 4800조 164억 9491만</t>
+    <t>1경 5448조 8236억 1870만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
@@ -971,7 +971,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%88%98%EC%B0%AC</t>
   </si>
   <si>
-    <t>2928조 3143억 4153만</t>
+    <t>3015조 2617억 9016만</t>
   </si>
   <si>
     <t>중탸치</t>
@@ -980,7 +980,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>2746조 1096억 4932만</t>
+    <t>2819조 3023억 850만</t>
   </si>
   <si>
     <t>서예슬</t>
@@ -1091,7 +1091,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
   </si>
   <si>
-    <t>199조 7463억 9040만</t>
+    <t>200조 476억 858만</t>
   </si>
   <si>
     <t>26퐝바</t>
@@ -1118,7 +1118,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
   </si>
   <si>
-    <t>166조 9906억 8312만</t>
+    <t>170조 9666억 5177만</t>
   </si>
   <si>
     <t>최씨용</t>
@@ -1127,7 +1127,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%94%A8%EC%9A%A9</t>
   </si>
   <si>
-    <t>165조 3399억 4755만</t>
+    <t>166조 4136억 2696만</t>
   </si>
   <si>
     <t>뻐늬</t>
@@ -1154,7 +1154,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%84%9D%EB%8F%99%ED%9A%8C%EC%A3%BC%EB%A8%B9</t>
   </si>
   <si>
-    <t>62조 4045억 7236만</t>
+    <t>62조 6296억 4429만</t>
+  </si>
+  <si>
+    <t>예라미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>50조 4366억 5518만</t>
   </si>
   <si>
     <t>서이따</t>
@@ -1166,15 +1175,6 @@
     <t>50조 3859억 842만</t>
   </si>
   <si>
-    <t>예라미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>50조 499억 6960만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%B9%98z</t>
   </si>
   <si>
@@ -1313,7 +1313,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%A7%84%EC%9F%81%EC%9D%B4</t>
   </si>
   <si>
-    <t>994조 8405억 3318만</t>
+    <t>1011조 8500억 8299만</t>
   </si>
   <si>
     <t>피치에이드</t>
@@ -1376,7 +1376,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A0%90</t>
   </si>
   <si>
-    <t>469조 8226억 287만</t>
+    <t>471조 3784억 5734만</t>
   </si>
   <si>
     <t>챠재범</t>
@@ -1385,7 +1385,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
   </si>
   <si>
-    <t>417조 8498억 1125만</t>
+    <t>427조 2462억 6528만</t>
   </si>
   <si>
     <t>사마련</t>
@@ -5182,7 +5182,7 @@
         <v>73</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>357</v>
@@ -5214,7 +5214,7 @@
         <v>73</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>360</v>
@@ -5403,10 +5403,10 @@
         <v>66</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>378</v>
@@ -5435,10 +5435,10 @@
         <v>66</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>253</v>
+        <v>193</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>381</v>
